--- a/administrative_forms/012_industrial_incident_form--administrative_forms.xlsx
+++ b/administrative_forms/012_industrial_incident_form--administrative_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="29" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -525,7 +525,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>industrial_incident_form_1_label</t>
+          <t>Incident Title</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -548,7 +548,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>incident_date</t>
+          <t>Incident Date</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -571,7 +571,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>incident_time</t>
+          <t>Incident Time</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -594,7 +594,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>incident_location</t>
+          <t>Incident Location</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -617,7 +617,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>incident_description</t>
+          <t>Incident Description</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -640,7 +640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>incident_cause</t>
+          <t>Incident Cause</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -663,7 +663,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>incident_effect</t>
+          <t>Incident Effect</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -686,7 +686,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>incident_severity</t>
+          <t>Incident Severity</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -709,7 +709,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>incident_reporter</t>
+          <t>Incident Reporter</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,7 +722,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>incident_date</t>
+          <t>Investigation Status</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,7 +745,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>incident_time</t>
+          <t>Investigation Conclusion</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -778,7 +778,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>incident_location</t>
+          <t>Root Cause Analysis</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -801,7 +801,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>incident_description</t>
+          <t>Prevention Plan</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -824,7 +824,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>incident_cause</t>
+          <t>Corrective Actions</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -847,7 +847,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>incident_effect</t>
+          <t>Review and Verification</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -860,7 +860,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -870,218 +870,11 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>incident_severity</t>
+          <t>Follow-up Actions</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>industrial_incident_form_17</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>incident_reporter</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>industrial_incident_form_18</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>incident_date</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>industrial_incident_form_19</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>incident_time</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>industrial_incident_form_20</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>incident_location</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>industrial_incident_form_21</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>incident_description</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>industrial_incident_form_22</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>incident_cause</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>industrial_incident_form_23</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>incident_effect</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>industrial_incident_form_24</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>incident_severity</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>industrial_incident_form_25</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>incident_reporter</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,12 +891,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="37" customWidth="1" min="1" max="1"/>
-    <col width="37" customWidth="1" min="2" max="2"/>
-    <col width="37" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +924,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'critical'}</t>
+          <t>critical</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 'Critical'}</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -1148,12 +941,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'major'}</t>
+          <t>major</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': 'Major'}</t>
+          <t>Major</t>
         </is>
       </c>
     </row>
@@ -1165,12 +958,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_'minor'}</t>
+          <t>minor</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': 'Minor'}</t>
+          <t>Minor</t>
         </is>
       </c>
     </row>
@@ -1182,12 +975,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'employee'}</t>
+          <t>employee</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 'Employee'}</t>
+          <t>Employee</t>
         </is>
       </c>
     </row>
@@ -1199,12 +992,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'supervisor'}</t>
+          <t>supervisor</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': 'Supervisor'}</t>
+          <t>Supervisor</t>
         </is>
       </c>
     </row>
@@ -1216,216 +1009,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_'manager'}</t>
+          <t>manager</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': 'Manager'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>industrial_incident_form_16_choices</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>{'value':_1,_'label':_'critical'}</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>{'value': 1, 'label': 'Critical'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>industrial_incident_form_16_choices</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>{'value':_2,_'label':_'major'}</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>{'value': 2, 'label': 'Major'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>industrial_incident_form_16_choices</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>{'value':_3,_'label':_'minor'}</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>{'value': 3, 'label': 'Minor'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>industrial_incident_form_17_choices</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>{'value':_1,_'label':_'employee'}</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>{'value': 1, 'label': 'Employee'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>industrial_incident_form_17_choices</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>{'value':_2,_'label':_'supervisor'}</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>{'value': 2, 'label': 'Supervisor'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>industrial_incident_form_17_choices</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>{'value':_3,_'label':_'manager'}</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>{'value': 3, 'label': 'Manager'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>industrial_incident_form_24_choices</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>{'value':_1,_'label':_'critical'}</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>{'value': 1, 'label': 'Critical'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>industrial_incident_form_24_choices</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>{'value':_2,_'label':_'major'}</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>{'value': 2, 'label': 'Major'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>industrial_incident_form_24_choices</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>{'value':_3,_'label':_'minor'}</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>{'value': 3, 'label': 'Minor'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>industrial_incident_form_25_choices</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>{'value':_1,_'label':_'employee'}</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>{'value': 1, 'label': 'Employee'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>industrial_incident_form_25_choices</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>{'value':_2,_'label':_'supervisor'}</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>{'value': 2, 'label': 'Supervisor'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>industrial_incident_form_25_choices</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>{'value':_3,_'label':_'manager'}</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>{'value': 3, 'label': 'Manager'}</t>
+          <t>Manager</t>
         </is>
       </c>
     </row>
